--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="67">
   <si>
     <t>Profile</t>
   </si>
@@ -47,6 +47,30 @@
     <t>Method</t>
   </si>
   <si>
+    <t>CPMVitalSignsObservation</t>
+  </si>
+  <si>
+    <t>CPM Vital Signs {Observation}</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-vital-signs (extensible)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
     <t>LabObservationChemhemtoxriaserObservation</t>
   </si>
   <si>
@@ -56,21 +80,12 @@
     <t>Observation Category Codes#laboratory</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
   </si>
   <si>
-    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>optional</t>
-  </si>
-  <si>
     <t>LabObservationCytopathologyObservation</t>
   </si>
   <si>
@@ -153,15 +168,6 @@
   </si>
   <si>
     <t>Vital Signs {Observation}</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#vital-signs</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-vital-signs (extensible)</t>
-  </si>
-  <si>
-    <t>dateTimeĵ, Periodĵ</t>
   </si>
   <si>
     <t>VitalSignsObservationConcentration</t>
@@ -340,7 +346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -421,7 +427,7 @@
         <v>20</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s" s="2">
         <v>14</v>
@@ -430,10 +436,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>17</v>
@@ -450,25 +456,25 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="D4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="C4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>15</v>
-      </c>
       <c r="G4" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>17</v>
@@ -485,25 +491,25 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s" s="2">
         <v>23</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>17</v>
@@ -520,13 +526,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>14</v>
@@ -535,10 +541,10 @@
         <v>14</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>17</v>
@@ -555,13 +561,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>14</v>
@@ -570,10 +576,10 @@
         <v>14</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>17</v>
@@ -590,13 +596,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>14</v>
@@ -605,10 +611,10 @@
         <v>14</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>17</v>
@@ -625,13 +631,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>14</v>
@@ -640,10 +646,10 @@
         <v>14</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>17</v>
@@ -660,13 +666,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>14</v>
@@ -675,10 +681,10 @@
         <v>14</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>17</v>
@@ -695,13 +701,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>14</v>
@@ -710,10 +716,10 @@
         <v>14</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>17</v>
@@ -730,13 +736,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>14</v>
@@ -745,10 +751,10 @@
         <v>14</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>17</v>
@@ -765,13 +771,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>14</v>
@@ -780,13 +786,13 @@
         <v>14</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -800,28 +806,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="C14" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="D14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s" s="2">
+      <c r="G14" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="H14" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>18</v>
@@ -841,19 +847,19 @@
         <v>51</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>17</v>
@@ -870,28 +876,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>18</v>
@@ -908,7 +914,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>14</v>
@@ -926,7 +932,7 @@
         <v>14</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
@@ -940,28 +946,28 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="F18" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -975,28 +981,28 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>18</v>
@@ -1013,7 +1019,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>14</v>
@@ -1022,7 +1028,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>14</v>
@@ -1031,7 +1037,7 @@
         <v>14</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -1045,28 +1051,28 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="C21" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>52</v>
-      </c>
       <c r="F21" t="s" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
@@ -1080,28 +1086,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
@@ -1118,7 +1124,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>14</v>
@@ -1136,7 +1142,7 @@
         <v>14</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
@@ -1150,28 +1156,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>64</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -1185,28 +1191,28 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -1223,7 +1229,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>14</v>
@@ -1232,7 +1238,7 @@
         <v>14</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>14</v>
@@ -1241,7 +1247,7 @@
         <v>14</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -1250,6 +1256,41 @@
         <v>14</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="77">
   <si>
     <t>Profile</t>
   </si>
@@ -144,6 +144,36 @@
   </si>
   <si>
     <t>Lab Observation: Surgical Pathology {Observation}</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultEchoObservation</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: Echo {Observation}</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#imaging</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes (extensible)</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultEKGObservation</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: EKG {Observation}</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultObservation</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result {Observation}</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultRadNucObservation</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: Rad/Nuc {Observation}</t>
   </si>
   <si>
     <t>SmokingStatusObservationObservation</t>
@@ -346,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -824,10 +854,10 @@
         <v>47</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>18</v>
@@ -841,13 +871,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>14</v>
@@ -856,10 +886,10 @@
         <v>14</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>17</v>
@@ -876,25 +906,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>17</v>
@@ -911,28 +941,28 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>53</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
@@ -946,28 +976,28 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="F18" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="G18" t="s" s="2">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -981,10 +1011,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -993,10 +1023,10 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>16</v>
@@ -1016,28 +1046,28 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -1054,7 +1084,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>14</v>
@@ -1063,7 +1093,7 @@
         <v>14</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>14</v>
@@ -1072,7 +1102,7 @@
         <v>14</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
@@ -1086,28 +1116,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>64</v>
-      </c>
       <c r="C22" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
@@ -1121,28 +1151,28 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
@@ -1159,7 +1189,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>14</v>
@@ -1168,7 +1198,7 @@
         <v>14</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>14</v>
@@ -1177,7 +1207,7 @@
         <v>14</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -1191,28 +1221,28 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -1226,28 +1256,28 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -1264,26 +1294,26 @@
         <v>14</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="C27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="F27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>56</v>
-      </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
       </c>
@@ -1291,6 +1321,146 @@
         <v>14</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K31" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="73">
   <si>
     <t>Profile</t>
   </si>
@@ -200,10 +200,28 @@
     <t>Vital Signs {Observation}</t>
   </si>
   <si>
-    <t>VitalSignsObservationConcentration</t>
-  </si>
-  <si>
-    <t>Vital Signs {Observation}: Concentration</t>
+    <t>VitalSignsObservationBP</t>
+  </si>
+  <si>
+    <t>Vital Signs {Observation}: BP</t>
+  </si>
+  <si>
+    <t>LOINC#85354-9</t>
+  </si>
+  <si>
+    <t>LOINC#8480-6</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>LOINC#8462-4</t>
+  </si>
+  <si>
+    <t>VitalSignsObservationSpO2</t>
+  </si>
+  <si>
+    <t>Vital Signs {Observation}: SpO2</t>
   </si>
   <si>
     <t>null#59408-5, null#2708-6</t>
@@ -212,37 +230,7 @@
     <t>LOINC#3151-8</t>
   </si>
   <si>
-    <t>Quantityĵ</t>
-  </si>
-  <si>
     <t>LOINC#3150-0</t>
-  </si>
-  <si>
-    <t>VitalSignsObservationdiastolic</t>
-  </si>
-  <si>
-    <t>Vital Signs {Observation}: diastolic</t>
-  </si>
-  <si>
-    <t>LOINC#85354-9</t>
-  </si>
-  <si>
-    <t>LOINC#8480-6</t>
-  </si>
-  <si>
-    <t>LOINC#8462-4</t>
-  </si>
-  <si>
-    <t>VitalSignsObservationFlow</t>
-  </si>
-  <si>
-    <t>Vital Signs {Observation}: Flow</t>
-  </si>
-  <si>
-    <t>VitalSignsObservationsystolic</t>
-  </si>
-  <si>
-    <t>Vital Signs {Observation}: systolic</t>
   </si>
 </sst>
 </file>
@@ -376,7 +364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1061,7 +1049,7 @@
         <v>64</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>16</v>
@@ -1166,7 +1154,7 @@
         <v>70</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>16</v>
@@ -1251,216 +1239,6 @@
         <v>14</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="F26" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="F27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="F28" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="F29" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D30" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="F30" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D31" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="F31" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K31" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -47,10 +47,10 @@
     <t>Method</t>
   </si>
   <si>
-    <t>CPMVitalSignsObservation</t>
-  </si>
-  <si>
-    <t>CPM Vital Signs {Observation}</t>
+    <t>CPMVitalSigns</t>
+  </si>
+  <si>
+    <t>CPM Vital Signs</t>
   </si>
   <si>
     <t>Observation Category Codes#vital-signs</t>
@@ -74,7 +74,7 @@
     <t>LabObservationChemhemtoxriaserObservation</t>
   </si>
   <si>
-    <t>Lab Observation: Chem, hem, tox, ria, ser {Observation}</t>
+    <t>Lab Observation: Chem, hem, tox, ria, ser Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory</t>
@@ -89,67 +89,67 @@
     <t>LabObservationCytopathologyObservation</t>
   </si>
   <si>
-    <t>Lab Observation: Cytopathology {Observation}</t>
+    <t>Lab Observation: Cytopathology Observation</t>
   </si>
   <si>
     <t>LabObservationElectronMicroscopyObservation</t>
   </si>
   <si>
-    <t>Lab Observation: Electron Microscopy {Observation}</t>
+    <t>Lab Observation: Electron Microscopy Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyBacteriologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycobacteriologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycobacteriology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycology Observation</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyObservation</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology {Observation}</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyObservationBacteriology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology {Observation}: Bacteriology</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyObservationMycobacteriology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology {Observation}: Mycobacteriology</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyObservationMycology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology {Observation}: Mycology</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyObservationParasitology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology {Observation}: Parasitology</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyObservationVirology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology {Observation}: Virology</t>
+    <t>Lab Observation: Microbiology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyParasitologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Parasitology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyVirologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Virology Observation</t>
   </si>
   <si>
     <t>LabObservationObservation</t>
   </si>
   <si>
-    <t>Lab Observation {Observation}</t>
+    <t>Lab Observation Observation</t>
   </si>
   <si>
     <t>LabObservationSurgicalPathologyObservation</t>
   </si>
   <si>
-    <t>Lab Observation: Surgical Pathology {Observation}</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultEchoObservation</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: Echo {Observation}</t>
+    <t>Lab Observation: Surgical Pathology Observation</t>
+  </si>
+  <si>
+    <t>ObservationImagingResult</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result</t>
   </si>
   <si>
     <t>Observation Category Codes#imaging</t>
@@ -158,28 +158,28 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes (extensible)</t>
   </si>
   <si>
-    <t>ObservationImagingResultEKGObservation</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: EKG {Observation}</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultObservation</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result {Observation}</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultRadNucObservation</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: Rad/Nuc {Observation}</t>
-  </si>
-  <si>
-    <t>SmokingStatusObservationObservation</t>
-  </si>
-  <si>
-    <t>Smoking Status Observation {Observation}</t>
+    <t>ObservationImagingResultEcho</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: Echo</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultEKG</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: EKG</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultRadNuc</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: Rad/Nuc</t>
+  </si>
+  <si>
+    <t>SmokingStatusObservation</t>
+  </si>
+  <si>
+    <t>Smoking Status Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#social-history</t>
@@ -194,34 +194,34 @@
     <t>CodeableConcept</t>
   </si>
   <si>
+    <t>VitalSignsBP</t>
+  </si>
+  <si>
+    <t>Vital Signs: BP</t>
+  </si>
+  <si>
+    <t>LOINC#85354-9</t>
+  </si>
+  <si>
+    <t>LOINC#8480-6</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>LOINC#8462-4</t>
+  </si>
+  <si>
     <t>VitalSignsObservation</t>
   </si>
   <si>
-    <t>Vital Signs {Observation}</t>
-  </si>
-  <si>
-    <t>VitalSignsObservationBP</t>
-  </si>
-  <si>
-    <t>Vital Signs {Observation}: BP</t>
-  </si>
-  <si>
-    <t>LOINC#85354-9</t>
-  </si>
-  <si>
-    <t>LOINC#8480-6</t>
-  </si>
-  <si>
-    <t>Quantityĵ</t>
-  </si>
-  <si>
-    <t>LOINC#8462-4</t>
-  </si>
-  <si>
-    <t>VitalSignsObservationSpO2</t>
-  </si>
-  <si>
-    <t>Vital Signs {Observation}: SpO2</t>
+    <t>Vital Signs Observation</t>
+  </si>
+  <si>
+    <t>VitalSignsSpO2</t>
+  </si>
+  <si>
+    <t>Vital Signs: SpO2</t>
   </si>
   <si>
     <t>null#59408-5, null#2708-6</t>
@@ -1011,10 +1011,10 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>16</v>
@@ -1034,28 +1034,28 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="C20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E20" t="s" s="2">
+      <c r="F20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H20" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -1072,7 +1072,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>14</v>
@@ -1090,7 +1090,7 @@
         <v>14</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
@@ -1104,28 +1104,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
@@ -1195,7 +1195,7 @@
         <v>14</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -1230,7 +1230,7 @@
         <v>14</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="75">
   <si>
     <t>Profile</t>
   </si>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>LOINC#8462-4</t>
+  </si>
+  <si>
+    <t>VitalSignsCPM</t>
+  </si>
+  <si>
+    <t>Vital Signs: CPM</t>
   </si>
   <si>
     <t>VitalSignsObservation</t>
@@ -364,7 +370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1151,7 +1157,7 @@
         <v>14</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>15</v>
@@ -1174,28 +1180,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -1212,7 +1218,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>14</v>
@@ -1221,7 +1227,7 @@
         <v>14</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>14</v>
@@ -1239,6 +1245,41 @@
         <v>14</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="67">
   <si>
     <t>Profile</t>
   </si>
@@ -47,177 +47,153 @@
     <t>Method</t>
   </si>
   <si>
-    <t>CPMVitalSigns</t>
-  </si>
-  <si>
-    <t>CPM Vital Signs</t>
+    <t>LabObservationChemhemtoxriaserObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Chem, hem, tox, ria, ser Observation</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#laboratory</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (extensible)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
+  </si>
+  <si>
+    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyBacteriologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycobacteriologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycobacteriology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyParasitologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Parasitology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyVirologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Virology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation Observation</t>
+  </si>
+  <si>
+    <t>ObservationImagingResult</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#imaging</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes (extensible)</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultEcho</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: Echo</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultEKG</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: EKG</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultRadNuc</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: Rad/Nuc</t>
+  </si>
+  <si>
+    <t>SmokingStatusObservation</t>
+  </si>
+  <si>
+    <t>Smoking Status Observation</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#social-history</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-smoking-status-observation-codes (extensible)</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>VitalSignsBP</t>
+  </si>
+  <si>
+    <t>Vital Signs BP</t>
   </si>
   <si>
     <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
-    <t/>
+    <t>LOINC#85354-9</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>LOINC#8480-6</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>LOINC#8462-4</t>
+  </si>
+  <si>
+    <t>VitalSignsCPM</t>
+  </si>
+  <si>
+    <t>Vital Signs: CPM</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-vital-signs (extensible)</t>
   </si>
   <si>
-    <t>dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>optional</t>
-  </si>
-  <si>
-    <t>LabObservationChemhemtoxriaserObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Chem, hem, tox, ria, ser Observation</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#laboratory</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (extensible)</t>
-  </si>
-  <si>
-    <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
-  </si>
-  <si>
-    <t>LabObservationCytopathologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Cytopathology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationElectronMicroscopyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Electron Microscopy Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyBacteriologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Bacteriology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyMycobacteriologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycobacteriology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyMycologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyParasitologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Parasitology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyVirologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Virology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation Observation</t>
-  </si>
-  <si>
-    <t>LabObservationSurgicalPathologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Surgical Pathology Observation</t>
-  </si>
-  <si>
-    <t>ObservationImagingResult</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#imaging</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes (extensible)</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultEcho</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: Echo</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultEKG</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: EKG</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultRadNuc</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: Rad/Nuc</t>
-  </si>
-  <si>
-    <t>SmokingStatusObservation</t>
-  </si>
-  <si>
-    <t>Smoking Status Observation</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#social-history</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-smoking-status-observation-codes (extensible)</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>CodeableConcept</t>
-  </si>
-  <si>
-    <t>VitalSignsBP</t>
-  </si>
-  <si>
-    <t>Vital Signs: BP</t>
-  </si>
-  <si>
-    <t>LOINC#85354-9</t>
-  </si>
-  <si>
-    <t>LOINC#8480-6</t>
-  </si>
-  <si>
-    <t>Quantityĵ</t>
-  </si>
-  <si>
-    <t>LOINC#8462-4</t>
-  </si>
-  <si>
-    <t>VitalSignsCPM</t>
-  </si>
-  <si>
-    <t>Vital Signs: CPM</t>
-  </si>
-  <si>
     <t>VitalSignsObservation</t>
   </si>
   <si>
@@ -227,7 +203,7 @@
     <t>VitalSignsSpO2</t>
   </si>
   <si>
-    <t>Vital Signs: SpO2</t>
+    <t>Vital Signs SpO2</t>
   </si>
   <si>
     <t>null#59408-5, null#2708-6</t>
@@ -370,7 +346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -451,7 +427,7 @@
         <v>20</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s" s="2">
         <v>14</v>
@@ -460,10 +436,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>17</v>
@@ -480,13 +456,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>14</v>
@@ -495,10 +471,10 @@
         <v>14</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>17</v>
@@ -515,13 +491,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>14</v>
@@ -530,10 +506,10 @@
         <v>14</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>17</v>
@@ -550,13 +526,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>14</v>
@@ -565,10 +541,10 @@
         <v>14</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>17</v>
@@ -585,13 +561,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>14</v>
@@ -600,10 +576,10 @@
         <v>14</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>17</v>
@@ -620,13 +596,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>14</v>
@@ -635,10 +611,10 @@
         <v>14</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>17</v>
@@ -655,13 +631,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>14</v>
@@ -670,10 +646,10 @@
         <v>14</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>17</v>
@@ -690,25 +666,25 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>22</v>
-      </c>
       <c r="G10" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>17</v>
@@ -725,13 +701,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>39</v>
-      </c>
       <c r="C11" t="s" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>14</v>
@@ -740,10 +716,10 @@
         <v>14</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>17</v>
@@ -760,13 +736,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>41</v>
-      </c>
       <c r="C12" t="s" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>14</v>
@@ -775,10 +751,10 @@
         <v>14</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>17</v>
@@ -795,13 +771,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>43</v>
-      </c>
       <c r="C13" t="s" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>14</v>
@@ -810,10 +786,10 @@
         <v>14</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>17</v>
@@ -830,28 +806,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="C14" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s" s="2">
+      <c r="G14" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="G14" t="s" s="2">
-        <v>23</v>
-      </c>
       <c r="H14" t="s" s="2">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>18</v>
@@ -865,25 +841,25 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>17</v>
@@ -900,28 +876,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>51</v>
-      </c>
       <c r="C16" t="s" s="2">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>18</v>
@@ -935,28 +911,28 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
@@ -970,13 +946,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>14</v>
@@ -985,13 +961,13 @@
         <v>14</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -1011,19 +987,19 @@
         <v>61</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>17</v>
@@ -1040,28 +1016,28 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -1078,7 +1054,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>14</v>
@@ -1096,7 +1072,7 @@
         <v>14</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
@@ -1110,28 +1086,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="F22" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
@@ -1140,146 +1116,6 @@
         <v>14</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F23" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K23" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="F26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K26" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -164,7 +164,7 @@
     <t>VitalSignsBP</t>
   </si>
   <si>
-    <t>Vital Signs BP</t>
+    <t>Vital Signs: BP</t>
   </si>
   <si>
     <t>Observation Category Codes#vital-signs</t>
@@ -203,7 +203,7 @@
     <t>VitalSignsSpO2</t>
   </si>
   <si>
-    <t>Vital Signs SpO2</t>
+    <t>Vital Signs: SpO2</t>
   </si>
   <si>
     <t>null#59408-5, null#2708-6</t>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="76">
   <si>
     <t>Profile</t>
   </si>
@@ -47,6 +47,27 @@
     <t>Method</t>
   </si>
   <si>
+    <t>ImmunizationObservation</t>
+  </si>
+  <si>
+    <t>Immunization Observation</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>LOINC#31044-1</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
     <t>LabObservationChemhemtoxriaserObservation</t>
   </si>
   <si>
@@ -56,9 +77,6 @@
     <t>Observation Category Codes#laboratory</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes (extensible)</t>
   </si>
   <si>
@@ -68,9 +86,6 @@
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>optional</t>
-  </si>
-  <si>
     <t>LabObservationMicrobiologyBacteriologyObservation</t>
   </si>
   <si>
@@ -111,6 +126,18 @@
   </si>
   <si>
     <t>Lab Observation Observation</t>
+  </si>
+  <si>
+    <t>ObservationEXAM</t>
+  </si>
+  <si>
+    <t>Observation EXAM</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#exam</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
     <t>ObservationImagingResult</t>
@@ -346,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -395,728 +422,798 @@
         <v>13</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>14</v>
       </c>
       <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="H2" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>17</v>
-      </c>
       <c r="I2" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="C3" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="D3" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="G4" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="C4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>16</v>
-      </c>
       <c r="H4" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="H11" t="s" s="2">
-        <v>17</v>
-      </c>
       <c r="I11" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="D14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="D14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s" s="2">
-        <v>46</v>
-      </c>
       <c r="G14" t="s" s="2">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="G20" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>53</v>
-      </c>
       <c r="H20" t="s" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="80">
   <si>
     <t>Profile</t>
   </si>
@@ -128,6 +128,9 @@
     <t>Lab Observation Observation</t>
   </si>
   <si>
+    <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>
+  </si>
+  <si>
     <t>ObservationEXAM</t>
   </si>
   <si>
@@ -146,18 +149,21 @@
     <t>Observation Imaging Result</t>
   </si>
   <si>
+    <t>Observation Category Codes#imaging, Observation Category Codes#imaging</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes (extensible)</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultEcho</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: Echo</t>
+  </si>
+  <si>
     <t>Observation Category Codes#imaging</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes (extensible)</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultEcho</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: Echo</t>
-  </si>
-  <si>
     <t>ObservationImagingResultEKG</t>
   </si>
   <si>
@@ -176,7 +182,7 @@
     <t>Smoking Status Observation</t>
   </si>
   <si>
-    <t>Observation Category Codes#social-history</t>
+    <t>Observation Category Codes#social-history, Observation Category Codes#social-history</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-smoking-status-observation-codes (extensible)</t>
@@ -225,6 +231,12 @@
   </si>
   <si>
     <t>Vital Signs Observation</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs, Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes (required)</t>
   </si>
   <si>
     <t>VitalSignsSpO2</t>
@@ -699,7 +711,7 @@
         <v>37</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>13</v>
@@ -728,13 +740,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>13</v>
@@ -743,7 +755,7 @@
         <v>13</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>15</v>
@@ -763,13 +775,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>13</v>
@@ -778,7 +790,7 @@
         <v>13</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>22</v>
@@ -798,22 +810,22 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>45</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>22</v>
@@ -833,14 +845,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="C14" t="s" s="2">
-        <v>44</v>
-      </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
       </c>
@@ -848,7 +860,7 @@
         <v>13</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>22</v>
@@ -868,13 +880,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>13</v>
@@ -883,7 +895,7 @@
         <v>13</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>22</v>
@@ -903,13 +915,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>13</v>
@@ -918,13 +930,13 @@
         <v>13</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>17</v>
@@ -938,25 +950,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>23</v>
@@ -976,7 +988,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -985,7 +997,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>13</v>
@@ -994,7 +1006,7 @@
         <v>13</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>17</v>
@@ -1011,7 +1023,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -1020,7 +1032,7 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>13</v>
@@ -1029,7 +1041,7 @@
         <v>13</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>17</v>
@@ -1043,13 +1055,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>13</v>
@@ -1058,10 +1070,10 @@
         <v>13</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>23</v>
@@ -1078,13 +1090,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
@@ -1093,10 +1105,10 @@
         <v>13</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>23</v>
@@ -1113,25 +1125,25 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>23</v>
@@ -1151,7 +1163,7 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1160,7 +1172,7 @@
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>13</v>
@@ -1169,7 +1181,7 @@
         <v>13</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1186,7 +1198,7 @@
         <v>13</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>13</v>
@@ -1195,7 +1207,7 @@
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>13</v>
@@ -1204,7 +1216,7 @@
         <v>13</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -68,10 +68,10 @@
     <t>optional</t>
   </si>
   <si>
-    <t>LabObservationChemhemtoxriaserObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Chem, hem, tox, ria, ser Observation</t>
+    <t>LaboratoryResultsChemhemtoxriaserObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Chem, hem, tox, ria, ser Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory</t>
@@ -86,46 +86,46 @@
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyBacteriologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Bacteriology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyMycobacteriologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycobacteriology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyMycologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyParasitologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Parasitology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyVirologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Virology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation Observation</t>
+    <t>LaboratoryResultsMicrobiologyBacteriologyObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Microbiology Bacteriology Observation</t>
+  </si>
+  <si>
+    <t>LaboratoryResultsMicrobiologyMycobacteriologyObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Microbiology Mycobacteriology Observation</t>
+  </si>
+  <si>
+    <t>LaboratoryResultsMicrobiologyMycologyObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Microbiology Mycology Observation</t>
+  </si>
+  <si>
+    <t>LaboratoryResultsMicrobiologyObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Microbiology Observation</t>
+  </si>
+  <si>
+    <t>LaboratoryResultsMicrobiologyParasitologyObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Microbiology Parasitology Observation</t>
+  </si>
+  <si>
+    <t>LaboratoryResultsMicrobiologyVirologyObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Microbiology Virology Observation</t>
+  </si>
+  <si>
+    <t>LaboratoryResultsObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="78">
   <si>
     <t>Profile</t>
   </si>
@@ -182,7 +182,7 @@
     <t>Smoking Status Observation</t>
   </si>
   <si>
-    <t>Observation Category Codes#social-history, Observation Category Codes#social-history</t>
+    <t>Observation Category Codes#social-history</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-smoking-status-observation-codes (extensible)</t>
@@ -194,16 +194,19 @@
     <t>CodeableConcept</t>
   </si>
   <si>
-    <t>VitalSignsBP</t>
-  </si>
-  <si>
-    <t>Vital Signs: BP</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#vital-signs</t>
-  </si>
-  <si>
-    <t>LOINC#85354-9</t>
+    <t>VitalSignsBPObservation</t>
+  </si>
+  <si>
+    <t>Vital Signs: BP Observation</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs, Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
+    <t>null#85354-9</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes (required)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>
@@ -218,13 +221,10 @@
     <t>LOINC#8462-4</t>
   </si>
   <si>
-    <t>VitalSignsCPM</t>
-  </si>
-  <si>
-    <t>Vital Signs: CPM</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-vital-signs (extensible)</t>
+    <t>VitalSignsCPMObservation</t>
+  </si>
+  <si>
+    <t>Vital Signs: CPM Observation</t>
   </si>
   <si>
     <t>VitalSignsObservation</t>
@@ -233,16 +233,10 @@
     <t>Vital Signs Observation</t>
   </si>
   <si>
-    <t>Observation Category Codes#vital-signs, Observation Category Codes#vital-signs</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes (required)</t>
-  </si>
-  <si>
-    <t>VitalSignsSpO2</t>
-  </si>
-  <si>
-    <t>Vital Signs: SpO2</t>
+    <t>VitalSignsSpO2Observation</t>
+  </si>
+  <si>
+    <t>Vital Signs: SpO2 Observation</t>
   </si>
   <si>
     <t>null#59408-5, null#2708-6</t>
@@ -965,10 +959,10 @@
         <v>63</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>23</v>
@@ -997,7 +991,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>13</v>
@@ -1006,7 +1000,7 @@
         <v>13</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>17</v>
@@ -1032,16 +1026,16 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="F19" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>66</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>17</v>
@@ -1055,10 +1049,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>62</v>
@@ -1070,10 +1064,10 @@
         <v>13</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>23</v>
@@ -1096,7 +1090,7 @@
         <v>72</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
@@ -1105,10 +1099,10 @@
         <v>13</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>23</v>
@@ -1125,10 +1119,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>62</v>
@@ -1137,13 +1131,13 @@
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>23</v>
@@ -1163,17 +1157,17 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="C23" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="F23" t="s" s="2">
         <v>13</v>
       </c>
@@ -1181,7 +1175,7 @@
         <v>13</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1198,7 +1192,7 @@
         <v>13</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>13</v>
@@ -1207,7 +1201,7 @@
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>13</v>
@@ -1216,7 +1210,7 @@
         <v>13</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="82">
   <si>
     <t>Profile</t>
   </si>
@@ -74,7 +74,7 @@
     <t>Laboratory Results: Chem, hem, tox, ria, ser Observation</t>
   </si>
   <si>
-    <t>Observation Category Codes#laboratory</t>
+    <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes (extensible)</t>
@@ -86,6 +86,18 @@
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
+    <t>LaboratoryResultsCytopathologyObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Cytopathology Observation</t>
+  </si>
+  <si>
+    <t>LaboratoryResultsElectronMicroscopyObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Electron Microscopy Observation</t>
+  </si>
+  <si>
     <t>LaboratoryResultsMicrobiologyBacteriologyObservation</t>
   </si>
   <si>
@@ -128,7 +140,10 @@
     <t>Laboratory Results Observation</t>
   </si>
   <si>
-    <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>
+    <t>LaboratoryResultsSurgicalPathologyObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Surgical Pathology Observation</t>
   </si>
   <si>
     <t>ObservationEXAM</t>
@@ -159,9 +174,6 @@
   </si>
   <si>
     <t>Observation Imaging Result: Echo</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#imaging</t>
   </si>
   <si>
     <t>ObservationImagingResultEKG</t>
@@ -379,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -705,7 +717,7 @@
         <v>37</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>13</v>
@@ -734,13 +746,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>40</v>
-      </c>
       <c r="C11" t="s" s="2">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>13</v>
@@ -749,13 +761,13 @@
         <v>13</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>17</v>
@@ -769,13 +781,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>13</v>
@@ -784,7 +796,7 @@
         <v>13</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>22</v>
@@ -804,13 +816,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>13</v>
@@ -819,7 +831,7 @@
         <v>13</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>22</v>
@@ -839,13 +851,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
@@ -854,13 +866,13 @@
         <v>13</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -874,13 +886,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>13</v>
@@ -889,7 +901,7 @@
         <v>13</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>22</v>
@@ -909,13 +921,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>13</v>
@@ -924,13 +936,13 @@
         <v>13</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>17</v>
@@ -944,25 +956,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>23</v>
@@ -979,28 +991,28 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>17</v>
@@ -1014,28 +1026,28 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="C19" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="F19" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="G19" t="s" s="2">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>17</v>
@@ -1049,25 +1061,25 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="G20" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>65</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>23</v>
@@ -1084,28 +1096,28 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>17</v>
@@ -1119,28 +1131,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>17</v>
@@ -1154,28 +1166,28 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1189,36 +1201,141 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="F24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K24" t="s" s="2">
+      <c r="B25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="82">
   <si>
     <t>Profile</t>
   </si>
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -606,13 +606,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>13</v>
@@ -621,13 +621,13 @@
         <v>13</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -641,10 +641,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>20</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>20</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>20</v>
@@ -746,10 +746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>20</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>20</v>
@@ -816,10 +816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>20</v>
@@ -851,13 +851,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
@@ -866,13 +866,13 @@
         <v>13</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -886,13 +886,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>13</v>
@@ -901,13 +901,13 @@
         <v>13</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>17</v>
@@ -921,10 +921,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>50</v>
@@ -956,10 +956,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>50</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>50</v>
@@ -1026,13 +1026,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>13</v>
@@ -1041,13 +1041,13 @@
         <v>13</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>17</v>
@@ -1061,28 +1061,28 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>17</v>
@@ -1096,28 +1096,28 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>65</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>17</v>
@@ -1143,7 +1143,7 @@
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>13</v>
@@ -1166,28 +1166,28 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1201,13 +1201,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>13</v>
@@ -1216,10 +1216,10 @@
         <v>13</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>23</v>
@@ -1236,25 +1236,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>23</v>
@@ -1274,7 +1274,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>13</v>
@@ -1283,7 +1283,7 @@
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>13</v>
@@ -1292,7 +1292,7 @@
         <v>13</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>17</v>
@@ -1306,36 +1306,491 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="C27" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E27" t="s" s="2">
+      <c r="C35" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="F27" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H27" t="s" s="2">
+      <c r="F37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="I27" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K27" t="s" s="2">
+      <c r="I37" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K40" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="84">
   <si>
     <t>Profile</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>LOINC#8462-4</t>
+  </si>
+  <si>
+    <t>LOINC#104158-1</t>
+  </si>
+  <si>
+    <t>LOINC#8358-4</t>
   </si>
   <si>
     <t>VitalSignsCPMObservation</t>
@@ -1213,7 +1219,7 @@
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>13</v>
@@ -1248,7 +1254,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>13</v>
@@ -1283,7 +1289,7 @@
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>13</v>
@@ -1306,10 +1312,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>66</v>
@@ -1344,7 +1350,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>13</v>
@@ -1353,7 +1359,7 @@
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>13</v>
@@ -1379,7 +1385,7 @@
         <v>13</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>13</v>
@@ -1388,7 +1394,7 @@
         <v>13</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>13</v>
@@ -1414,16 +1420,16 @@
         <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>13</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>13</v>
@@ -1446,10 +1452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>66</v>
@@ -1484,7 +1490,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>13</v>
@@ -1493,7 +1499,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>13</v>
@@ -1519,7 +1525,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1528,7 +1534,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1554,7 +1560,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1563,7 +1569,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>13</v>
@@ -1586,10 +1592,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>66</v>
@@ -1598,7 +1604,7 @@
         <v>13</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>68</v>
@@ -1624,7 +1630,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1633,7 +1639,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>13</v>
@@ -1659,7 +1665,7 @@
         <v>13</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>13</v>
@@ -1668,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>13</v>
@@ -1694,7 +1700,7 @@
         <v>13</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>13</v>
@@ -1703,7 +1709,7 @@
         <v>13</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>13</v>
@@ -1729,7 +1735,7 @@
         <v>13</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1738,7 +1744,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>13</v>
@@ -1764,7 +1770,7 @@
         <v>13</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>13</v>
@@ -1773,7 +1779,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>13</v>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="82">
   <si>
     <t>Profile</t>
   </si>
@@ -237,12 +237,6 @@
   </si>
   <si>
     <t>LOINC#8358-4</t>
-  </si>
-  <si>
-    <t>VitalSignsCPMObservation</t>
-  </si>
-  <si>
-    <t>Vital Signs: CPM Observation</t>
   </si>
   <si>
     <t>VitalSignsObservation</t>
@@ -397,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1464,7 +1458,7 @@
         <v>13</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>68</v>
@@ -1499,7 +1493,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>13</v>
@@ -1508,7 +1502,7 @@
         <v>13</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>17</v>
@@ -1534,7 +1528,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1543,7 +1537,7 @@
         <v>13</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>17</v>
@@ -1569,7 +1563,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>13</v>
@@ -1592,25 +1586,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>23</v>
@@ -1630,7 +1624,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1639,7 +1633,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>13</v>
@@ -1648,7 +1642,7 @@
         <v>13</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>17</v>
@@ -1657,146 +1651,6 @@
         <v>13</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="F37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F39" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="F40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K40" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="84">
   <si>
     <t>Profile</t>
   </si>
@@ -68,22 +68,28 @@
     <t>optional</t>
   </si>
   <si>
+    <t>LaboratoryResults</t>
+  </si>
+  <si>
+    <t>Laboratory Results</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (extensible)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
+  </si>
+  <si>
+    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
     <t>LaboratoryResultsChemhemtoxriaserObservation</t>
   </si>
   <si>
     <t>Laboratory Results: Chem, hem, tox, ria, ser Observation</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (extensible)</t>
-  </si>
-  <si>
-    <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
-  </si>
-  <si>
-    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
     <t>LaboratoryResultsCytopathologyObservation</t>
@@ -391,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -606,13 +612,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>13</v>
@@ -621,13 +627,13 @@
         <v>13</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -641,13 +647,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>31</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>13</v>
@@ -656,13 +662,13 @@
         <v>13</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>17</v>
@@ -892,7 +898,7 @@
         <v>45</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>13</v>
@@ -901,13 +907,13 @@
         <v>13</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>17</v>
@@ -921,28 +927,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="B16" t="s" s="2">
+      <c r="D16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="C16" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s" s="2">
-        <v>51</v>
-      </c>
       <c r="G16" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>17</v>
@@ -956,22 +962,22 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="B17" t="s" s="2">
+      <c r="D17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>22</v>
@@ -997,7 +1003,7 @@
         <v>55</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>13</v>
@@ -1006,7 +1012,7 @@
         <v>13</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>22</v>
@@ -1032,7 +1038,7 @@
         <v>57</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>13</v>
@@ -1041,7 +1047,7 @@
         <v>13</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>22</v>
@@ -1067,7 +1073,7 @@
         <v>59</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>13</v>
@@ -1076,13 +1082,13 @@
         <v>13</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>17</v>
@@ -1096,28 +1102,28 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G21" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B21" t="s" s="2">
+      <c r="H21" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="F21" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>17</v>
@@ -1131,28 +1137,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F22" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="F22" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="G22" t="s" s="2">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>17</v>
@@ -1169,7 +1175,7 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1187,7 +1193,7 @@
         <v>13</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1204,7 +1210,7 @@
         <v>13</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>13</v>
@@ -1213,16 +1219,16 @@
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>
@@ -1239,7 +1245,7 @@
         <v>13</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>13</v>
@@ -1248,7 +1254,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>13</v>
@@ -1274,7 +1280,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>13</v>
@@ -1283,7 +1289,7 @@
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>13</v>
@@ -1306,25 +1312,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="C27" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="F27" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>23</v>
@@ -1341,25 +1347,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>23</v>
@@ -1379,7 +1385,7 @@
         <v>13</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>13</v>
@@ -1388,7 +1394,7 @@
         <v>13</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>13</v>
@@ -1414,7 +1420,7 @@
         <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>13</v>
@@ -1423,7 +1429,7 @@
         <v>13</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>13</v>
@@ -1446,25 +1452,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>23</v>
@@ -1481,28 +1487,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>17</v>
@@ -1519,7 +1525,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1528,7 +1534,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1537,7 +1543,7 @@
         <v>13</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>17</v>
@@ -1554,7 +1560,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1563,16 +1569,16 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="F34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>17</v>
@@ -1589,7 +1595,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1598,7 +1604,7 @@
         <v>13</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>13</v>
@@ -1624,7 +1630,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1633,7 +1639,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>13</v>
@@ -1651,6 +1657,41 @@
         <v>13</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K37" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="82">
   <si>
     <t>Profile</t>
   </si>
@@ -68,10 +68,10 @@
     <t>optional</t>
   </si>
   <si>
-    <t>LaboratoryResults</t>
-  </si>
-  <si>
-    <t>Laboratory Results</t>
+    <t>LaboratoryResultsChemhemtoxriaserObservation</t>
+  </si>
+  <si>
+    <t>Laboratory Results: Chem, hem, tox, ria, ser Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>
@@ -84,12 +84,6 @@
   </si>
   <si>
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsChemhemtoxriaserObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Chem, hem, tox, ria, ser Observation</t>
   </si>
   <si>
     <t>LaboratoryResultsCytopathologyObservation</t>
@@ -397,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -612,13 +606,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>13</v>
@@ -627,13 +621,13 @@
         <v>13</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -647,13 +641,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>31</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>13</v>
@@ -662,13 +656,13 @@
         <v>13</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>17</v>
@@ -898,7 +892,7 @@
         <v>45</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>13</v>
@@ -907,13 +901,13 @@
         <v>13</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>17</v>
@@ -927,13 +921,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>13</v>
@@ -942,13 +936,13 @@
         <v>13</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>17</v>
@@ -962,22 +956,22 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="B17" t="s" s="2">
+      <c r="D17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s" s="2">
-        <v>53</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>22</v>
@@ -1003,7 +997,7 @@
         <v>55</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>13</v>
@@ -1012,7 +1006,7 @@
         <v>13</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>22</v>
@@ -1038,7 +1032,7 @@
         <v>57</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>13</v>
@@ -1047,7 +1041,7 @@
         <v>13</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>22</v>
@@ -1073,7 +1067,7 @@
         <v>59</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>13</v>
@@ -1082,13 +1076,13 @@
         <v>13</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>17</v>
@@ -1102,28 +1096,28 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>17</v>
@@ -1137,28 +1131,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>17</v>
@@ -1175,7 +1169,7 @@
         <v>13</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1193,7 +1187,7 @@
         <v>13</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1210,7 +1204,7 @@
         <v>13</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>13</v>
@@ -1219,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>13</v>
@@ -1228,7 +1222,7 @@
         <v>13</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>
@@ -1245,7 +1239,7 @@
         <v>13</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>13</v>
@@ -1254,7 +1248,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>13</v>
@@ -1280,7 +1274,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>13</v>
@@ -1289,7 +1283,7 @@
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>13</v>
@@ -1312,25 +1306,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>23</v>
@@ -1347,25 +1341,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>23</v>
@@ -1385,7 +1379,7 @@
         <v>13</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>13</v>
@@ -1394,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>13</v>
@@ -1420,7 +1414,7 @@
         <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>13</v>
@@ -1429,7 +1423,7 @@
         <v>13</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>13</v>
@@ -1452,25 +1446,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>23</v>
@@ -1487,28 +1481,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="C32" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D32" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="F32" t="s" s="2">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>17</v>
@@ -1525,7 +1519,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1534,7 +1528,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1543,7 +1537,7 @@
         <v>13</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>17</v>
@@ -1560,7 +1554,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1569,7 +1563,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>13</v>
@@ -1578,7 +1572,7 @@
         <v>13</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>17</v>
@@ -1595,7 +1589,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1604,7 +1598,7 @@
         <v>13</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>13</v>
@@ -1630,7 +1624,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1639,7 +1633,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>13</v>
@@ -1657,41 +1651,6 @@
         <v>13</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K37" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="67">
   <si>
     <t>Profile</t>
   </si>
@@ -68,10 +68,10 @@
     <t>optional</t>
   </si>
   <si>
-    <t>LaboratoryResultsChemhemtoxriaserObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Chem, hem, tox, ria, ser Observation</t>
+    <t>LabObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>
@@ -86,76 +86,49 @@
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>LaboratoryResultsCytopathologyObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Cytopathology Observation</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsElectronMicroscopyObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Electron Microscopy Observation</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsMicrobiologyBacteriologyObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Microbiology Bacteriology Observation</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsMicrobiologyMycobacteriologyObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Microbiology Mycobacteriology Observation</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsMicrobiologyMycologyObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Microbiology Mycology Observation</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsMicrobiologyObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Microbiology Observation</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsMicrobiologyParasitologyObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Microbiology Parasitology Observation</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsMicrobiologyVirologyObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Microbiology Virology Observation</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results Observation</t>
-  </si>
-  <si>
-    <t>LaboratoryResultsSurgicalPathologyObservation</t>
-  </si>
-  <si>
-    <t>Laboratory Results: Surgical Pathology Observation</t>
-  </si>
-  <si>
-    <t>ObservationEXAM</t>
-  </si>
-  <si>
-    <t>Observation EXAM</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#exam</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+    <t>LabObservationChemhemtoxriaserObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Chem, hem, tox, ria, ser Observation</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#laboratory</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyBacteriology</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycobacteriology</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycobacteriology</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycology</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycology</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyParasitology</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Parasitology</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyVirology</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Virology</t>
   </si>
   <si>
     <t>ObservationImagingResult</t>
@@ -164,28 +137,10 @@
     <t>Observation Imaging Result</t>
   </si>
   <si>
-    <t>Observation Category Codes#imaging, Observation Category Codes#imaging</t>
+    <t>Observation Category Codes#imaging</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes (extensible)</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultEcho</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: Echo</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultEKG</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: EKG</t>
-  </si>
-  <si>
-    <t>ObservationImagingResultRadNuc</t>
-  </si>
-  <si>
-    <t>Observation Imaging Result: Rad/Nuc</t>
   </si>
   <si>
     <t>SmokingStatusObservation</t>
@@ -391,7 +346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -507,7 +462,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>13</v>
@@ -536,13 +491,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>13</v>
@@ -571,13 +526,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>13</v>
@@ -606,13 +561,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>13</v>
@@ -621,13 +576,13 @@
         <v>13</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -641,13 +596,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>13</v>
@@ -676,13 +631,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>13</v>
@@ -711,13 +666,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>13</v>
@@ -746,13 +701,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>13</v>
@@ -761,7 +716,7 @@
         <v>13</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>22</v>
@@ -781,13 +736,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>13</v>
@@ -796,13 +751,13 @@
         <v>13</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>17</v>
@@ -816,25 +771,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>23</v>
@@ -851,28 +806,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -886,28 +841,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>17</v>
@@ -921,25 +876,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>23</v>
@@ -956,25 +911,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>23</v>
@@ -991,25 +946,25 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>23</v>
@@ -1026,13 +981,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>13</v>
@@ -1041,10 +996,10 @@
         <v>13</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>23</v>
@@ -1061,28 +1016,28 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="F20" t="s" s="2">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>17</v>
@@ -1096,25 +1051,25 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>23</v>
@@ -1134,7 +1089,7 @@
         <v>13</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1143,7 +1098,7 @@
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>13</v>
@@ -1152,7 +1107,7 @@
         <v>13</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>17</v>
@@ -1166,28 +1121,28 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1204,17 +1159,17 @@
         <v>13</v>
       </c>
       <c r="B24" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="C24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="F24" t="s" s="2">
         <v>13</v>
       </c>
@@ -1222,7 +1177,7 @@
         <v>13</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>
@@ -1239,7 +1194,7 @@
         <v>13</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>13</v>
@@ -1248,7 +1203,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>13</v>
@@ -1257,7 +1212,7 @@
         <v>13</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>17</v>
@@ -1274,7 +1229,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>13</v>
@@ -1283,7 +1238,7 @@
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>13</v>
@@ -1306,25 +1261,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>23</v>
@@ -1344,7 +1299,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>13</v>
@@ -1353,7 +1308,7 @@
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>13</v>
@@ -1371,286 +1326,6 @@
         <v>13</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="F30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="D31" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F31" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D32" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="F32" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="F33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="F36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K36" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="100">
   <si>
     <t>Profile</t>
   </si>
@@ -68,10 +68,10 @@
     <t>optional</t>
   </si>
   <si>
-    <t>LabObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation</t>
+    <t>LabObservationChemhemtoxriaserObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Chem, hem, tox, ria, ser Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>
@@ -86,31 +86,73 @@
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>LabObservationChemhemtoxriaserObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Chem, hem, tox, ria, ser Observation</t>
+    <t>LabObservationCytopathologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Cytopathology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationElectronMicroscopyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Electron Microscopy Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyBacteriologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyBacteriologyObservation-bacteria</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observation-bacteria</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyBacteriology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Bacteriology</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyMycobacteriology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycobacteriology</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyMycology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycology</t>
+    <t>LabObservationMicrobiologyBacteriologyObservation-gramstain</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observation-gramstain</t>
+  </si>
+  <si>
+    <t>LOINC#664-3</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycobacteriologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycobacteriology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycobacteriologyObservation-acidfast</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycobacteriology Observation-acidfast</t>
+  </si>
+  <si>
+    <t>LOINC#11545-1</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycobacteriologyObservation-mycobact</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycobacteriology Observation-mycobact</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyMycologyObservation-fungus</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycology Observation-fungus</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyObservation</t>
@@ -119,16 +161,55 @@
     <t>Lab Observation: Microbiology Observation</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyParasitology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Parasitology</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyVirology</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Virology</t>
+    <t>LabObservationMicrobiologyParasitologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Parasitology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyParasitologyObservation-parasite</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Parasitology Observation-parasite</t>
+  </si>
+  <si>
+    <t>[not stated]#1000</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyVirologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Virology Observation</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyVirologyObservation-virus</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Virology Observation-virus</t>
+  </si>
+  <si>
+    <t>LabObservationObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation Observation</t>
+  </si>
+  <si>
+    <t>LabObservationSurgicalPathologyObservation</t>
+  </si>
+  <si>
+    <t>Lab Observation: Surgical Pathology Observation</t>
+  </si>
+  <si>
+    <t>ObservationEXAM</t>
+  </si>
+  <si>
+    <t>Observation EXAM</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#exam</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
     <t>ObservationImagingResult</t>
@@ -137,10 +218,28 @@
     <t>Observation Imaging Result</t>
   </si>
   <si>
-    <t>Observation Category Codes#imaging</t>
+    <t>Observation Category Codes#imaging, Observation Category Codes#imaging</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes (extensible)</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultEcho</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: Echo</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultEKG</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: EKG</t>
+  </si>
+  <si>
+    <t>ObservationImagingResultRadNuc</t>
+  </si>
+  <si>
+    <t>Observation Imaging Result: Rad/Nuc</t>
   </si>
   <si>
     <t>SmokingStatusObservation</t>
@@ -346,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -462,7 +561,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>13</v>
@@ -491,13 +590,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>28</v>
-      </c>
       <c r="C5" t="s" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>13</v>
@@ -526,13 +625,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B6" t="s" s="2">
-        <v>30</v>
-      </c>
       <c r="C6" t="s" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>13</v>
@@ -561,13 +660,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>13</v>
@@ -576,13 +675,13 @@
         <v>13</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -596,13 +695,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>13</v>
@@ -631,22 +730,22 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B9" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="F9" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>22</v>
@@ -666,13 +765,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>38</v>
-      </c>
       <c r="C10" t="s" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>13</v>
@@ -701,22 +800,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="C11" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="F11" t="s" s="2">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>22</v>
@@ -736,13 +835,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>13</v>
@@ -751,13 +850,13 @@
         <v>13</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>17</v>
@@ -771,25 +870,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>23</v>
@@ -806,28 +905,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -841,28 +940,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>17</v>
@@ -876,25 +975,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>50</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>23</v>
@@ -911,25 +1010,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>23</v>
@@ -946,25 +1045,25 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>23</v>
@@ -981,13 +1080,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>13</v>
@@ -996,10 +1095,10 @@
         <v>13</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>23</v>
@@ -1016,25 +1115,25 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>23</v>
@@ -1051,25 +1150,25 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>61</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>23</v>
@@ -1086,28 +1185,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>17</v>
@@ -1121,25 +1220,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>23</v>
@@ -1156,28 +1255,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>
@@ -1191,28 +1290,28 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>17</v>
@@ -1226,25 +1325,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>23</v>
@@ -1261,28 +1360,28 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>17</v>
@@ -1296,25 +1395,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>23</v>
@@ -1326,6 +1425,531 @@
         <v>13</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="103">
   <si>
     <t>Profile</t>
   </si>
@@ -122,6 +122,18 @@
     <t>LOINC#664-3</t>
   </si>
   <si>
+    <t>LabObservationMicrobiologyBacteriologyObservation-sputum</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observation-sputum</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyBacteriologyObservation-unire</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observation-unire</t>
+  </si>
+  <si>
     <t>LabObservationMicrobiologyMycobacteriologyObservation</t>
   </si>
   <si>
@@ -173,9 +185,6 @@
     <t>Lab Observation: Microbiology Parasitology Observation-parasite</t>
   </si>
   <si>
-    <t>[not stated]#1000</t>
-  </si>
-  <si>
     <t>LabObservationMicrobiologyVirologyObservation</t>
   </si>
   <si>
@@ -260,24 +269,36 @@
     <t>CodeableConcept</t>
   </si>
   <si>
-    <t>VitalSignsBPObservation</t>
-  </si>
-  <si>
-    <t>Vital Signs: BP Observation</t>
+    <t>VitalSigns</t>
+  </si>
+  <si>
+    <t>Vital Signs</t>
   </si>
   <si>
     <t>Observation Category Codes#vital-signs, Observation Category Codes#vital-signs</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes (required)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>LOINC#104158-1</t>
+  </si>
+  <si>
+    <t>LOINC#8358-4</t>
+  </si>
+  <si>
+    <t>VitalSignsBP</t>
+  </si>
+  <si>
+    <t>Vital Signs: BP</t>
+  </si>
+  <si>
     <t>null#85354-9</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes (required)</t>
-  </si>
-  <si>
-    <t>dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
     <t>LOINC#8480-6</t>
   </si>
   <si>
@@ -287,22 +308,10 @@
     <t>LOINC#8462-4</t>
   </si>
   <si>
-    <t>LOINC#104158-1</t>
-  </si>
-  <si>
-    <t>LOINC#8358-4</t>
-  </si>
-  <si>
-    <t>VitalSignsObservation</t>
-  </si>
-  <si>
-    <t>Vital Signs Observation</t>
-  </si>
-  <si>
-    <t>VitalSignsSpO2Observation</t>
-  </si>
-  <si>
-    <t>Vital Signs: SpO2 Observation</t>
+    <t>VitalSignsSpO2</t>
+  </si>
+  <si>
+    <t>Vital Signs: SpO2</t>
   </si>
   <si>
     <t>null#59408-5, null#2708-6</t>
@@ -445,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -771,7 +780,7 @@
         <v>37</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>13</v>
@@ -812,10 +821,10 @@
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>22</v>
@@ -835,13 +844,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>42</v>
-      </c>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>13</v>
@@ -870,22 +879,22 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="C13" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="C13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="F13" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>22</v>
@@ -981,7 +990,7 @@
         <v>50</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>13</v>
@@ -1016,16 +1025,16 @@
         <v>52</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>22</v>
@@ -1045,10 +1054,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>55</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>20</v>
@@ -1080,10 +1089,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>32</v>
@@ -1115,10 +1124,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>20</v>
@@ -1150,13 +1159,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="B21" t="s" s="2">
-        <v>61</v>
-      </c>
       <c r="C21" t="s" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
@@ -1185,13 +1194,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>63</v>
-      </c>
       <c r="C22" t="s" s="2">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>13</v>
@@ -1200,13 +1209,13 @@
         <v>13</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>17</v>
@@ -1220,13 +1229,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>13</v>
@@ -1235,7 +1244,7 @@
         <v>13</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>22</v>
@@ -1255,28 +1264,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>69</v>
-      </c>
       <c r="G24" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>
@@ -1290,22 +1299,22 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>22</v>
@@ -1325,13 +1334,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="C26" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>13</v>
@@ -1340,7 +1349,7 @@
         <v>13</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>22</v>
@@ -1360,13 +1369,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="B27" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="C27" t="s" s="2">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>13</v>
@@ -1375,13 +1384,13 @@
         <v>13</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>17</v>
@@ -1395,25 +1404,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>23</v>
@@ -1430,28 +1439,28 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G29" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="C29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="F29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="H29" t="s" s="2">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>17</v>
@@ -1465,28 +1474,28 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>17</v>
@@ -1503,7 +1512,7 @@
         <v>13</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>13</v>
@@ -1512,7 +1521,7 @@
         <v>13</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>13</v>
@@ -1538,7 +1547,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>13</v>
@@ -1547,7 +1556,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>13</v>
@@ -1573,7 +1582,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1582,7 +1591,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1605,25 +1614,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="B34" t="s" s="2">
+      <c r="C34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="C34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="F34" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>23</v>
@@ -1643,7 +1652,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1652,7 +1661,7 @@
         <v>13</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>13</v>
@@ -1661,7 +1670,7 @@
         <v>13</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>17</v>
@@ -1678,7 +1687,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1687,7 +1696,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>13</v>
@@ -1696,7 +1705,7 @@
         <v>13</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>17</v>
@@ -1713,7 +1722,7 @@
         <v>13</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>13</v>
@@ -1722,7 +1731,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>13</v>
@@ -1745,25 +1754,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>23</v>
@@ -1783,7 +1792,7 @@
         <v>13</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1792,7 +1801,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>13</v>
@@ -1801,7 +1810,7 @@
         <v>13</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>17</v>
@@ -1815,28 +1824,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>17</v>
@@ -1853,25 +1862,25 @@
         <v>13</v>
       </c>
       <c r="B41" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="F41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>17</v>
@@ -1888,25 +1897,25 @@
         <v>13</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E42" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="F42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>17</v>
@@ -1923,7 +1932,7 @@
         <v>13</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>13</v>
@@ -1932,7 +1941,7 @@
         <v>13</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>13</v>
@@ -1950,6 +1959,76 @@
         <v>13</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K45" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -128,10 +128,10 @@
     <t>Lab Observation: Microbiology Bacteriology Observation-sputum</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyBacteriologyObservation-unire</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Bacteriology Observation-unire</t>
+    <t>LabObservationMicrobiologyBacteriologyObservation-urine</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observation-urine</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyMycobacteriologyObservation</t>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -296,7 +296,7 @@
     <t>Vital Signs: BP</t>
   </si>
   <si>
-    <t>null#85354-9</t>
+    <t>LOINC#85354-9</t>
   </si>
   <si>
     <t>LOINC#8480-6</t>
@@ -1629,7 +1629,7 @@
         <v>94</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -104,34 +104,34 @@
     <t>Lab Observation: Microbiology Bacteriology Observation</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyBacteriologyObservation-bacteria</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Bacteriology Observation-bacteria</t>
+    <t>LabObservationMicrobiologyBacteriologyObservationbacteria</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observationbacteria</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyBacteriologyObservation-gramstain</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Bacteriology Observation-gramstain</t>
+    <t>LabObservationMicrobiologyBacteriologyObservationgramstain</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observationgramstain</t>
   </si>
   <si>
     <t>LOINC#664-3</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyBacteriologyObservation-sputum</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Bacteriology Observation-sputum</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyBacteriologyObservation-urine</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Bacteriology Observation-urine</t>
+    <t>LabObservationMicrobiologyBacteriologyObservationsputum</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observationsputum</t>
+  </si>
+  <si>
+    <t>LabObservationMicrobiologyBacteriologyObservationurine</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Bacteriology Observationurine</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyMycobacteriologyObservation</t>
@@ -140,19 +140,19 @@
     <t>Lab Observation: Microbiology Mycobacteriology Observation</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyMycobacteriologyObservation-acidfast</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycobacteriology Observation-acidfast</t>
+    <t>LabObservationMicrobiologyMycobacteriologyObservationacidfast</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycobacteriology Observationacidfast</t>
   </si>
   <si>
     <t>LOINC#11545-1</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyMycobacteriologyObservation-mycobact</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycobacteriology Observation-mycobact</t>
+    <t>LabObservationMicrobiologyMycobacteriologyObservationmycobact</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycobacteriology Observationmycobact</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyMycologyObservation</t>
@@ -161,10 +161,10 @@
     <t>Lab Observation: Microbiology Mycology Observation</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyMycologyObservation-fungus</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycology Observation-fungus</t>
+    <t>LabObservationMicrobiologyMycologyObservationfungus</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycology Observationfungus</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyObservation</t>
@@ -179,10 +179,10 @@
     <t>Lab Observation: Microbiology Parasitology Observation</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyParasitologyObservation-parasite</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Parasitology Observation-parasite</t>
+    <t>LabObservationMicrobiologyParasitologyObservationparasite</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Parasitology Observationparasite</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyVirologyObservation</t>
@@ -191,10 +191,10 @@
     <t>Lab Observation: Microbiology Virology Observation</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyVirologyObservation-virus</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Virology Observation-virus</t>
+    <t>LabObservationMicrobiologyVirologyObservationvirus</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Virology Observationvirus</t>
   </si>
   <si>
     <t>LabObservationObservation</t>
@@ -296,7 +296,7 @@
     <t>Vital Signs: BP</t>
   </si>
   <si>
-    <t>LOINC#85354-9</t>
+    <t>null#85354-9</t>
   </si>
   <si>
     <t>LOINC#8480-6</t>
@@ -1629,7 +1629,7 @@
         <v>94</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="101">
   <si>
     <t>Profile</t>
   </si>
@@ -177,12 +177,6 @@
   </si>
   <si>
     <t>Lab Observation: Microbiology Parasitology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyParasitologyObservationparasite</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Parasitology Observationparasite</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyVirologyObservation</t>
@@ -454,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1095,7 +1089,7 @@
         <v>56</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>13</v>
@@ -1130,7 +1124,7 @@
         <v>58</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>13</v>
@@ -1165,7 +1159,7 @@
         <v>60</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
@@ -1235,7 +1229,7 @@
         <v>64</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>13</v>
@@ -1244,13 +1238,13 @@
         <v>13</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1264,13 +1258,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>13</v>
@@ -1279,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>
@@ -1299,22 +1293,22 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="B25" t="s" s="2">
+      <c r="D25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s" s="2">
         <v>70</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>22</v>
@@ -1340,7 +1334,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>13</v>
@@ -1349,7 +1343,7 @@
         <v>13</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>22</v>
@@ -1375,7 +1369,7 @@
         <v>76</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>13</v>
@@ -1384,7 +1378,7 @@
         <v>13</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>22</v>
@@ -1410,7 +1404,7 @@
         <v>78</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>13</v>
@@ -1419,13 +1413,13 @@
         <v>13</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>17</v>
@@ -1439,13 +1433,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>13</v>
@@ -1454,13 +1448,13 @@
         <v>13</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>17</v>
@@ -1474,25 +1468,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>23</v>
@@ -1512,7 +1506,7 @@
         <v>13</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>13</v>
@@ -1521,7 +1515,7 @@
         <v>13</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>13</v>
@@ -1547,7 +1541,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>13</v>
@@ -1556,7 +1550,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>13</v>
@@ -1579,25 +1573,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="F33" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="C33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="F33" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="G33" t="s" s="2">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>23</v>
@@ -1614,28 +1608,28 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="C34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E34" t="s" s="2">
+      <c r="F34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="F34" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>17</v>
@@ -1652,7 +1646,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1670,7 +1664,7 @@
         <v>13</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>17</v>
@@ -1687,7 +1681,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1696,7 +1690,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>13</v>
@@ -1705,7 +1699,7 @@
         <v>13</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>17</v>
@@ -1722,7 +1716,7 @@
         <v>13</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>13</v>
@@ -1731,7 +1725,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>13</v>
@@ -1757,7 +1751,7 @@
         <v>13</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>13</v>
@@ -1766,7 +1760,7 @@
         <v>13</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>13</v>
@@ -1789,25 +1783,25 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>23</v>
@@ -1824,28 +1818,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="C40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>17</v>
@@ -1862,7 +1856,7 @@
         <v>13</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>13</v>
@@ -1871,7 +1865,7 @@
         <v>13</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>13</v>
@@ -1880,7 +1874,7 @@
         <v>13</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>17</v>
@@ -1897,7 +1891,7 @@
         <v>13</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>13</v>
@@ -1906,7 +1900,7 @@
         <v>13</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>13</v>
@@ -1915,7 +1909,7 @@
         <v>13</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>17</v>
@@ -1932,7 +1926,7 @@
         <v>13</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>13</v>
@@ -1941,7 +1935,7 @@
         <v>13</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>13</v>
@@ -1967,7 +1961,7 @@
         <v>13</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>13</v>
@@ -1976,7 +1970,7 @@
         <v>13</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>13</v>
@@ -1994,41 +1988,6 @@
         <v>13</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="F45" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K45" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -107,7 +107,7 @@
     <t>LabObservationMicrobiologyBacteriologyObservationbacteria</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Bacteriology Observationbacteria</t>
+    <t>Lab Observation: Microbiology Bacteriology Observation[bacteria]</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory</t>
@@ -116,7 +116,7 @@
     <t>LabObservationMicrobiologyBacteriologyObservationgramstain</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Bacteriology Observationgramstain</t>
+    <t>Lab Observation: Microbiology Bacteriology Observation[gramstain]</t>
   </si>
   <si>
     <t>LOINC#664-3</t>
@@ -125,13 +125,13 @@
     <t>LabObservationMicrobiologyBacteriologyObservationsputum</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Bacteriology Observationsputum</t>
+    <t>Lab Observation: Microbiology Bacteriology Observation[sputum]</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyBacteriologyObservationurine</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Bacteriology Observationurine</t>
+    <t>Lab Observation: Microbiology Bacteriology Observation[urine]</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyMycobacteriologyObservation</t>
@@ -143,7 +143,7 @@
     <t>LabObservationMicrobiologyMycobacteriologyObservationacidfast</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Mycobacteriology Observationacidfast</t>
+    <t>Lab Observation: Microbiology Mycobacteriology Observation[acidfast]</t>
   </si>
   <si>
     <t>LOINC#11545-1</t>
@@ -152,7 +152,7 @@
     <t>LabObservationMicrobiologyMycobacteriologyObservationmycobact</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Mycobacteriology Observationmycobact</t>
+    <t>Lab Observation: Microbiology Mycobacteriology Observation[mycobact]</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyMycologyObservation</t>
@@ -164,7 +164,7 @@
     <t>LabObservationMicrobiologyMycologyObservationfungus</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Mycology Observationfungus</t>
+    <t>Lab Observation: Microbiology Mycology Observation[fungus]</t>
   </si>
   <si>
     <t>LabObservationMicrobiologyObservation</t>
@@ -188,7 +188,7 @@
     <t>LabObservationMicrobiologyVirologyObservationvirus</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Virology Observationvirus</t>
+    <t>Lab Observation: Microbiology Virology Observation[virus]</t>
   </si>
   <si>
     <t>LabObservationObservation</t>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="101">
   <si>
     <t>Profile</t>
   </si>
@@ -281,25 +281,25 @@
     <t>LOINC#104158-1</t>
   </si>
   <si>
+    <t>VitalSignsBP</t>
+  </si>
+  <si>
+    <t>Vital Signs: BP</t>
+  </si>
+  <si>
+    <t>null#85354-9</t>
+  </si>
+  <si>
+    <t>LOINC#8480-6</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>LOINC#8462-4</t>
+  </si>
+  <si>
     <t>LOINC#8358-4</t>
-  </si>
-  <si>
-    <t>VitalSignsBP</t>
-  </si>
-  <si>
-    <t>Vital Signs: BP</t>
-  </si>
-  <si>
-    <t>null#85354-9</t>
-  </si>
-  <si>
-    <t>LOINC#8480-6</t>
-  </si>
-  <si>
-    <t>Quantityĵ</t>
-  </si>
-  <si>
-    <t>LOINC#8462-4</t>
   </si>
   <si>
     <t>VitalSignsSpO2</t>
@@ -448,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1538,25 +1538,25 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>23</v>
@@ -1573,13 +1573,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="B33" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="C33" t="s" s="2">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>13</v>
@@ -1588,13 +1588,13 @@
         <v>92</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>17</v>
@@ -1611,7 +1611,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1620,16 +1620,16 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="F34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>17</v>
@@ -1646,7 +1646,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1664,7 +1664,7 @@
         <v>13</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>17</v>
@@ -1681,7 +1681,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1716,7 +1716,7 @@
         <v>13</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>13</v>
@@ -1748,25 +1748,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>23</v>
@@ -1783,28 +1783,28 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>97</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>17</v>
@@ -1830,7 +1830,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>13</v>
@@ -1839,7 +1839,7 @@
         <v>13</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>17</v>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>13</v>
@@ -1874,7 +1874,7 @@
         <v>13</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>17</v>
@@ -1918,76 +1918,6 @@
         <v>13</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D43" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D44" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E44" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K44" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -272,7 +272,7 @@
     <t>Observation Category Codes#vital-signs, Observation Category Codes#vital-signs</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes (required)</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsCodes (required)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="97">
   <si>
     <t>Profile</t>
   </si>
@@ -161,12 +161,6 @@
     <t>Lab Observation: Microbiology Mycology Observation</t>
   </si>
   <si>
-    <t>LabObservationMicrobiologyMycologyObservationfungus</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Mycology Observation[fungus]</t>
-  </si>
-  <si>
     <t>LabObservationMicrobiologyObservation</t>
   </si>
   <si>
@@ -183,12 +177,6 @@
   </si>
   <si>
     <t>Lab Observation: Microbiology Virology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationMicrobiologyVirologyObservationvirus</t>
-  </si>
-  <si>
-    <t>Lab Observation: Microbiology Virology Observation[virus]</t>
   </si>
   <si>
     <t>LabObservationObservation</t>
@@ -448,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -984,7 +972,7 @@
         <v>50</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>13</v>
@@ -1124,7 +1112,7 @@
         <v>58</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>13</v>
@@ -1159,7 +1147,7 @@
         <v>60</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
@@ -1168,13 +1156,13 @@
         <v>13</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>17</v>
@@ -1188,13 +1176,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>13</v>
@@ -1203,7 +1191,7 @@
         <v>13</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>22</v>
@@ -1223,10 +1211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>65</v>
@@ -1241,10 +1229,10 @@
         <v>66</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -1258,13 +1246,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>13</v>
@@ -1273,7 +1261,7 @@
         <v>13</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>22</v>
@@ -1299,7 +1287,7 @@
         <v>72</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>13</v>
@@ -1308,7 +1296,7 @@
         <v>13</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>22</v>
@@ -1334,7 +1322,7 @@
         <v>74</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>13</v>
@@ -1343,13 +1331,13 @@
         <v>13</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>17</v>
@@ -1363,13 +1351,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>13</v>
@@ -1378,10 +1366,10 @@
         <v>13</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>23</v>
@@ -1398,28 +1386,28 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>17</v>
@@ -1433,25 +1421,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="C29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="F29" t="s" s="2">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>23</v>
@@ -1468,25 +1456,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>23</v>
@@ -1506,7 +1494,7 @@
         <v>13</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>13</v>
@@ -1524,7 +1512,7 @@
         <v>13</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>17</v>
@@ -1538,28 +1526,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="D32" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="F32" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>17</v>
@@ -1576,7 +1564,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1585,7 +1573,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1594,7 +1582,7 @@
         <v>13</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>17</v>
@@ -1611,7 +1599,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1620,7 +1608,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>13</v>
@@ -1629,7 +1617,7 @@
         <v>13</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>17</v>
@@ -1646,7 +1634,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>13</v>
@@ -1655,7 +1643,7 @@
         <v>13</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>13</v>
@@ -1678,25 +1666,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>23</v>
@@ -1716,7 +1704,7 @@
         <v>13</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>13</v>
@@ -1725,7 +1713,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>13</v>
@@ -1734,7 +1722,7 @@
         <v>13</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>17</v>
@@ -1748,28 +1736,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="B38" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="F38" t="s" s="2">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>17</v>
@@ -1786,7 +1774,7 @@
         <v>13</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1795,7 +1783,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>13</v>
@@ -1804,7 +1792,7 @@
         <v>13</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>17</v>
@@ -1821,7 +1809,7 @@
         <v>13</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>13</v>
@@ -1830,7 +1818,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>13</v>
@@ -1839,7 +1827,7 @@
         <v>13</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>17</v>
@@ -1848,76 +1836,6 @@
         <v>13</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="F41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="F42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K42" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="95">
   <si>
     <t>Profile</t>
   </si>
@@ -86,18 +86,6 @@
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>LabObservationCytopathologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Cytopathology Observation</t>
-  </si>
-  <si>
-    <t>LabObservationElectronMicroscopyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Electron Microscopy Observation</t>
-  </si>
-  <si>
     <t>LabObservationMicrobiologyBacteriologyObservation</t>
   </si>
   <si>
@@ -161,6 +149,12 @@
     <t>Lab Observation: Microbiology Mycology Observation</t>
   </si>
   <si>
+    <t>LabObservationMicrobiologyMycologyObservationfungus</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Mycology Observation[fungus]</t>
+  </si>
+  <si>
     <t>LabObservationMicrobiologyObservation</t>
   </si>
   <si>
@@ -179,16 +173,16 @@
     <t>Lab Observation: Microbiology Virology Observation</t>
   </si>
   <si>
+    <t>LabObservationMicrobiologyVirologyObservationvirus</t>
+  </si>
+  <si>
+    <t>Lab Observation: Microbiology Virology Observation[virus]</t>
+  </si>
+  <si>
     <t>LabObservationObservation</t>
   </si>
   <si>
     <t>Lab Observation Observation</t>
-  </si>
-  <si>
-    <t>LabObservationSurgicalPathologyObservation</t>
-  </si>
-  <si>
-    <t>Lab Observation: Surgical Pathology Observation</t>
   </si>
   <si>
     <t>ObservationEXAM</t>
@@ -436,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -581,13 +575,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>13</v>
@@ -596,13 +590,13 @@
         <v>13</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -616,13 +610,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>13</v>
@@ -651,28 +645,28 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -686,13 +680,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>13</v>
@@ -721,22 +715,22 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>22</v>
@@ -762,7 +756,7 @@
         <v>37</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>13</v>
@@ -797,16 +791,16 @@
         <v>39</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>22</v>
@@ -826,13 +820,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>13</v>
@@ -861,22 +855,22 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>22</v>
@@ -902,7 +896,7 @@
         <v>46</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
@@ -1042,7 +1036,7 @@
         <v>54</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>13</v>
@@ -1112,7 +1106,7 @@
         <v>58</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>13</v>
@@ -1121,13 +1115,13 @@
         <v>13</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>17</v>
@@ -1141,13 +1135,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>13</v>
@@ -1156,13 +1150,13 @@
         <v>13</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>17</v>
@@ -1176,22 +1170,22 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="B22" t="s" s="2">
+      <c r="D22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s" s="2">
-        <v>66</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>22</v>
@@ -1217,7 +1211,7 @@
         <v>68</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>13</v>
@@ -1226,7 +1220,7 @@
         <v>13</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>22</v>
@@ -1252,7 +1246,7 @@
         <v>70</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>13</v>
@@ -1261,7 +1255,7 @@
         <v>13</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>22</v>
@@ -1287,7 +1281,7 @@
         <v>72</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>13</v>
@@ -1296,13 +1290,13 @@
         <v>13</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>17</v>
@@ -1316,13 +1310,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>13</v>
@@ -1331,13 +1325,13 @@
         <v>13</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>17</v>
@@ -1351,25 +1345,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>23</v>
@@ -1389,7 +1383,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>13</v>
@@ -1398,7 +1392,7 @@
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>13</v>
@@ -1421,25 +1415,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="C29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="F29" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="G29" t="s" s="2">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>23</v>
@@ -1456,28 +1450,28 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="C30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E30" t="s" s="2">
+      <c r="F30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="F30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>17</v>
@@ -1494,7 +1488,7 @@
         <v>13</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>13</v>
@@ -1512,7 +1506,7 @@
         <v>13</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>17</v>
@@ -1529,7 +1523,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>13</v>
@@ -1538,7 +1532,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>13</v>
@@ -1547,7 +1541,7 @@
         <v>13</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>17</v>
@@ -1564,7 +1558,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1573,7 +1567,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1599,7 +1593,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1608,7 +1602,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>13</v>
@@ -1631,25 +1625,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>23</v>
@@ -1666,28 +1660,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="C36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>17</v>
@@ -1704,7 +1698,7 @@
         <v>13</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>13</v>
@@ -1713,7 +1707,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>13</v>
@@ -1722,7 +1716,7 @@
         <v>13</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>17</v>
@@ -1739,7 +1733,7 @@
         <v>13</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>13</v>
@@ -1748,7 +1742,7 @@
         <v>13</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>13</v>
@@ -1757,7 +1751,7 @@
         <v>13</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>17</v>
@@ -1774,7 +1768,7 @@
         <v>13</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1783,7 +1777,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>13</v>
@@ -1801,41 +1795,6 @@
         <v>13</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="F40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K40" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/docs/observations-summary.xlsx
+++ b/docs/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="94">
   <si>
     <t>Profile</t>
   </si>
@@ -74,7 +74,7 @@
     <t>Lab Observation: Chem, hem, tox, ria, ser Observation</t>
   </si>
   <si>
-    <t>Observation Category Codes#laboratory, Observation Category Codes#laboratory</t>
+    <t>Observation Category Codes#laboratory</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes (extensible)</t>
@@ -98,9 +98,6 @@
     <t>Lab Observation: Microbiology Bacteriology Observation[bacteria]</t>
   </si>
   <si>
-    <t>Observation Category Codes#laboratory</t>
-  </si>
-  <si>
     <t>LabObservationMicrobiologyBacteriologyObservationgramstain</t>
   </si>
   <si>
@@ -203,7 +200,7 @@
     <t>Observation Imaging Result</t>
   </si>
   <si>
-    <t>Observation Category Codes#imaging, Observation Category Codes#imaging</t>
+    <t>Observation Category Codes#imaging</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes (extensible)</t>
@@ -616,7 +613,7 @@
         <v>27</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>13</v>
@@ -645,19 +642,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>31</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
@@ -680,13 +677,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B8" t="s" s="2">
-        <v>33</v>
-      </c>
       <c r="C8" t="s" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>13</v>
@@ -715,13 +712,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B9" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="C9" t="s" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>13</v>
@@ -750,10 +747,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>37</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>20</v>
@@ -785,19 +782,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>40</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>13</v>
@@ -820,13 +817,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>42</v>
-      </c>
       <c r="C12" t="s" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>13</v>
@@ -855,10 +852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>44</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>20</v>
@@ -890,13 +887,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>46</v>
-      </c>
       <c r="C14" t="s" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
@@ -925,10 +922,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>20</v>
@@ -960,10 +957,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>50</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>20</v>
@@ -995,10 +992,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>52</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>20</v>
@@ -1030,13 +1027,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="B18" t="s" s="2">
-        <v>54</v>
-      </c>
       <c r="C18" t="s" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>13</v>
@@ -1065,10 +1062,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>55</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>56</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>20</v>
@@ -1100,22 +1097,22 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="C20" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="C20" t="s" s="2">
+      <c r="D20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>60</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>15</v>
@@ -1135,22 +1132,22 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="B21" t="s" s="2">
+      <c r="C21" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="D21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s" s="2">
-        <v>64</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>22</v>
@@ -1170,22 +1167,22 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>66</v>
-      </c>
       <c r="C22" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s" s="2">
-        <v>64</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>22</v>
@@ -1205,22 +1202,22 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="B23" t="s" s="2">
-        <v>68</v>
-      </c>
       <c r="C23" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s" s="2">
-        <v>64</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>22</v>
@@ -1240,22 +1237,22 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="B24" t="s" s="2">
-        <v>70</v>
-      </c>
       <c r="C24" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>64</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>22</v>
@@ -1275,28 +1272,28 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="B25" t="s" s="2">
+      <c r="C25" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="C25" t="s" s="2">
+      <c r="D25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="D25" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s" s="2">
+      <c r="G25" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="G25" t="s" s="2">
+      <c r="H25" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>17</v>
@@ -1310,25 +1307,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="B26" t="s" s="2">
+      <c r="C26" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="C26" t="s" s="2">
+      <c r="D26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="D26" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s" s="2">
+      <c r="G26" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>23</v>
@@ -1348,7 +1345,7 @@
         <v>13</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>13</v>
@@ -1357,7 +1354,7 @@
         <v>13</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>13</v>
@@ -1383,7 +1380,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>13</v>
@@ -1392,7 +1389,7 @@
         <v>13</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>13</v>
@@ -1415,25 +1412,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="B29" t="s" s="2">
+      <c r="C29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="C29" t="s" s="2">
+      <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="D29" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F29" t="s" s="2">
+      <c r="G29" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>23</v>
@@ -1453,7 +1450,7 @@
         <v>13</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>13</v>
@@ -1462,16 +1459,16 @@
         <v>13</v>
       </c>
       <c r="E30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="F30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>17</v>
@@ -1488,7 +1485,7 @@
         <v>13</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>13</v>
@@ -1497,7 +1494,7 @@
         <v>13</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>13</v>
@@ -1506,7 +1503,7 @@
         <v>13</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>17</v>
@@ -1523,7 +1520,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>13</v>
@@ -1532,7 +1529,7 @@
         <v>13</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>13</v>
@@ -1558,7 +1555,7 @@
         <v>13</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>13</v>
@@ -1567,7 +1564,7 @@
         <v>13</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>13</v>
@@ -1593,7 +1590,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>13</v>
@@ -1602,7 +1599,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>13</v>
@@ -1625,25 +1622,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="B35" t="s" s="2">
+      <c r="C35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="C35" t="s" s="2">
+      <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="D35" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="F35" t="s" s="2">
+      <c r="G35" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>23</v>
@@ -1663,7 +1660,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>13</v>
@@ -1672,7 +1669,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>13</v>
@@ -1681,7 +1678,7 @@
         <v>13</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>17</v>
@@ -1698,7 +1695,7 @@
         <v>13</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>13</v>
@@ -1707,7 +1704,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>13</v>
@@ -1716,7 +1713,7 @@
         <v>13</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>17</v>
@@ -1733,7 +1730,7 @@
         <v>13</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>13</v>
@@ -1742,7 +1739,7 @@
         <v>13</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>13</v>
@@ -1768,7 +1765,7 @@
         <v>13</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>13</v>
@@ -1777,7 +1774,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>13</v>
